--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/ARIZONA_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/ARIZONA_2023.xlsx
@@ -4056,7 +4056,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C206">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C335">
@@ -21984,7 +21984,7 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1202">
